--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jun-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15.72</v>
+        <v>709.34</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>240.243</v>
+        <v>10840.59</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>828.235</v>
+        <v>37372.82</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>836.726</v>
+        <v>37755.97</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30.716</v>
+        <v>1386.01</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9828.143955</v>
+        <v>443479.78</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>693.304</v>
+        <v>31284.27</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>105.312</v>
+        <v>4752.04</v>
       </c>
     </row>
     <row r="10">
@@ -1061,11 +1061,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17716.55</v>
+        <v>799431.89</v>
       </c>
     </row>
     <row r="11">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>24280.998</v>
+        <v>1095642.44</v>
       </c>
     </row>
     <row r="12">
@@ -1187,11 +1187,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>177.714</v>
+        <v>8019.07</v>
       </c>
     </row>
     <row r="13">
@@ -1248,11 +1248,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>160.162</v>
+        <v>7227.06</v>
       </c>
     </row>
     <row r="14">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6230.959952</v>
+        <v>281162.42</v>
       </c>
     </row>
     <row r="15">
@@ -1374,11 +1374,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1132.104</v>
+        <v>51084.44</v>
       </c>
     </row>
     <row r="16">
@@ -1435,11 +1435,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>230.37</v>
+        <v>10395.09</v>
       </c>
     </row>
     <row r="17">
@@ -1496,11 +1496,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6976.92</v>
+        <v>314822.71</v>
       </c>
     </row>
     <row r="18">
@@ -1557,11 +1557,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>89.45399999999999</v>
+        <v>4036.47</v>
       </c>
     </row>
     <row r="19">
@@ -1618,11 +1618,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26.999</v>
+        <v>1218.29</v>
       </c>
     </row>
     <row r="20">
@@ -1679,11 +1679,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>830.429</v>
+        <v>37471.82</v>
       </c>
     </row>
     <row r="21">
@@ -1740,11 +1740,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1362.474</v>
+        <v>61479.53</v>
       </c>
     </row>
   </sheetData>
